--- a/prompts/prompt.xlsx
+++ b/prompts/prompt.xlsx
@@ -1,122 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\steve\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="29145" windowHeight="16050"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="说明" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="元提示词" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="AI 交易系统提示词" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="软件工程，glue coding 用提示词" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="终极本质分析" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="前端通用设计" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="面向CZ" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="学习用提示词" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="临界知识" sheetId="9" r:id="rId13"/>
-    <sheet state="visible" name="根据内容逆向提示词" sheetId="10" r:id="rId14"/>
-    <sheet state="visible" name="逻辑工具箱" sheetId="11" r:id="rId15"/>
-    <sheet state="visible" name="哲学工具箱" sheetId="12" r:id="rId16"/>
-    <sheet state="visible" name="方法与原则提取" sheetId="13" r:id="rId17"/>
-    <sheet state="visible" name="排版" sheetId="14" r:id="rId18"/>
-    <sheet state="visible" name="图像特征提取" sheetId="15" r:id="rId19"/>
-    <sheet state="visible" name="Reddit提示词" sheetId="16" r:id="rId20"/>
-    <sheet state="visible" name="ChatGPT" sheetId="17" r:id="rId21"/>
-    <sheet state="visible" name="论文解读" sheetId="18" r:id="rId22"/>
-    <sheet state="visible" name="内容提炼" sheetId="19" r:id="rId23"/>
-    <sheet state="visible" name="英文学习" sheetId="20" r:id="rId24"/>
-    <sheet state="visible" name="问题分类识别" sheetId="21" r:id="rId25"/>
-    <sheet state="visible" name="用户优化前端设计" sheetId="22" r:id="rId26"/>
-    <sheet state="visible" name="最小知识框架" sheetId="23" r:id="rId27"/>
-    <sheet state="visible" name="事实核查" sheetId="24" r:id="rId28"/>
-    <sheet state="visible" name="关键词图谱" sheetId="25" r:id="rId29"/>
-    <sheet state="visible" name="语言分析元prompt" sheetId="26" r:id="rId30"/>
-    <sheet state="visible" name="逻辑分析" sheetId="27" r:id="rId31"/>
-    <sheet state="visible" name="一句话描述任何内容" sheetId="28" r:id="rId32"/>
-    <sheet state="visible" name="输入转单行JSON" sheetId="29" r:id="rId33"/>
-    <sheet state="visible" name="最小字数系统提示词" sheetId="30" r:id="rId34"/>
-    <sheet state="visible" name="需求对齐" sheetId="31" r:id="rId35"/>
-    <sheet state="visible" name="编程知识库" sheetId="32" r:id="rId36"/>
-    <sheet state="visible" name="提示词模块" sheetId="33" r:id="rId37"/>
-    <sheet state="visible" name="x爆款文案生成器" sheetId="34" r:id="rId38"/>
-    <sheet state="visible" name="grok商业金融分析提示词" sheetId="35" r:id="rId39"/>
-    <sheet state="visible" name="文本转md语法电子书处理" sheetId="36" r:id="rId40"/>
-    <sheet state="visible" name="ai学习用提示词" sheetId="37" r:id="rId41"/>
-    <sheet state="visible" name="真传一句话" sheetId="38" r:id="rId42"/>
-    <sheet state="visible" name="需求结构化描述" sheetId="39" r:id="rId43"/>
-    <sheet state="visible" name="学习提示词" sheetId="40" r:id="rId44"/>
-    <sheet state="visible" name="系统提示词" sheetId="41" r:id="rId45"/>
-    <sheet state="visible" name="排版和图片，视频转文本" sheetId="42" r:id="rId46"/>
-    <sheet state="visible" name="子弹总结" sheetId="43" r:id="rId47"/>
-    <sheet state="visible" name="x提示词收集" sheetId="44" r:id="rId48"/>
-    <sheet state="visible" name="书籍结构化分析" sheetId="45" r:id="rId49"/>
-    <sheet state="visible" name="组织语言" sheetId="46" r:id="rId50"/>
-    <sheet state="visible" name="行业分析" sheetId="47" r:id="rId51"/>
-    <sheet state="visible" name="投资调研" sheetId="48" r:id="rId52"/>
-    <sheet state="visible" name="速成学习" sheetId="49" r:id="rId53"/>
-    <sheet state="visible" name="批判性思维分析" sheetId="50" r:id="rId54"/>
-    <sheet state="visible" name="序列图生成" sheetId="51" r:id="rId55"/>
-    <sheet state="visible" name="对话提问" sheetId="52" r:id="rId56"/>
-    <sheet state="visible" name="层级结构分析" sheetId="53" r:id="rId57"/>
-    <sheet state="visible" name="心经口诀创作提示词" sheetId="54" r:id="rId58"/>
-    <sheet state="visible" name="SOP制作" sheetId="55" r:id="rId59"/>
-    <sheet state="visible" name="黄金圈解释" sheetId="56" r:id="rId60"/>
-    <sheet state="visible" name="需求解析" sheetId="57" r:id="rId61"/>
-    <sheet state="visible" name="notebookllm用提示词" sheetId="58" r:id="rId62"/>
-    <sheet state="visible" name="好prompt生成器" sheetId="59" r:id="rId63"/>
-    <sheet state="visible" name="行业咨询" sheetId="60" r:id="rId64"/>
-    <sheet state="visible" name="分析" sheetId="61" r:id="rId65"/>
-    <sheet state="visible" name="gemini字幕处理" sheetId="62" r:id="rId66"/>
-    <sheet state="visible" name="政治批判工具箱" sheetId="63" r:id="rId67"/>
-    <sheet state="visible" name="推文制作提示词" sheetId="64" r:id="rId68"/>
-    <sheet state="visible" name="麦肯锡行业分析" sheetId="65" r:id="rId69"/>
-    <sheet state="visible" name="正向人物生平报告官方文案" sheetId="66" r:id="rId70"/>
-    <sheet state="visible" name="grok抓取提示词" sheetId="67" r:id="rId71"/>
-    <sheet state="visible" name="视频生成提示词" sheetId="68" r:id="rId72"/>
-    <sheet state="visible" name="人话写作" sheetId="69" r:id="rId73"/>
-    <sheet state="visible" name="x prompt收集" sheetId="70" r:id="rId74"/>
-    <sheet state="visible" name="函数化万物" sheetId="71" r:id="rId75"/>
-    <sheet state="visible" name="项目分析" sheetId="72" r:id="rId76"/>
-    <sheet state="visible" name="解释提示词" sheetId="73" r:id="rId77"/>
-    <sheet state="visible" name="产品策略" sheetId="74" r:id="rId78"/>
-    <sheet state="visible" name="小红书" sheetId="75" r:id="rId79"/>
-    <sheet state="visible" name="谋士" sheetId="76" r:id="rId80"/>
-    <sheet state="visible" name="前端复刻流程" sheetId="77" r:id="rId81"/>
-    <sheet state="visible" name="网页UI逆向分析提示词" sheetId="78" r:id="rId82"/>
-    <sheet state="visible" name="典籍句子学习" sheetId="79" r:id="rId83"/>
-    <sheet state="visible" name="经验" sheetId="80" r:id="rId84"/>
-    <sheet state="visible" name="anki卡片格式输出" sheetId="81" r:id="rId85"/>
-    <sheet state="visible" name="简讯提示词" sheetId="82" r:id="rId86"/>
-    <sheet state="visible" name="思维导图" sheetId="83" r:id="rId87"/>
-    <sheet state="visible" name="未来视角" sheetId="84" r:id="rId88"/>
-    <sheet state="visible" name="AI使用思维" sheetId="85" r:id="rId89"/>
-    <sheet state="visible" name="思维协议" sheetId="86" r:id="rId90"/>
-    <sheet state="visible" name="李继刚文选" sheetId="87" r:id="rId91"/>
-    <sheet state="visible" name="图片逆向" sheetId="88" r:id="rId92"/>
-    <sheet state="visible" name="艺术风格描述" sheetId="89" r:id="rId93"/>
-    <sheet state="visible" name="豆包听书" sheetId="90" r:id="rId94"/>
-    <sheet state="visible" name="艺术" sheetId="91" r:id="rId95"/>
-    <sheet state="visible" name="文案逆向" sheetId="92" r:id="rId96"/>
-    <sheet state="visible" name="流程图" sheetId="93" r:id="rId97"/>
-    <sheet state="visible" name="学习音频" sheetId="94" r:id="rId98"/>
-    <sheet state="visible" name="思维模型" sheetId="95" r:id="rId99"/>
-    <sheet state="visible" name="道" sheetId="96" r:id="rId100"/>
-    <sheet state="visible" name="法" sheetId="97" r:id="rId101"/>
-    <sheet state="visible" name="术" sheetId="98" r:id="rId102"/>
-    <sheet state="visible" name="器" sheetId="99" r:id="rId103"/>
+    <sheet name="说明" sheetId="1" r:id="rId1"/>
+    <sheet name="元提示词" sheetId="2" r:id="rId2"/>
+    <sheet name="AI 交易系统提示词" sheetId="3" r:id="rId3"/>
+    <sheet name="软件工程，glue coding 用提示词" sheetId="4" r:id="rId4"/>
+    <sheet name="终极本质分析" sheetId="5" r:id="rId5"/>
+    <sheet name="前端通用设计" sheetId="6" r:id="rId6"/>
+    <sheet name="面向CZ" sheetId="7" r:id="rId7"/>
+    <sheet name="学习用提示词" sheetId="8" r:id="rId8"/>
+    <sheet name="临界知识" sheetId="9" r:id="rId9"/>
+    <sheet name="根据内容逆向提示词" sheetId="10" r:id="rId10"/>
+    <sheet name="逻辑工具箱" sheetId="11" r:id="rId11"/>
+    <sheet name="哲学工具箱" sheetId="12" r:id="rId12"/>
+    <sheet name="方法与原则提取" sheetId="13" r:id="rId13"/>
+    <sheet name="排版" sheetId="14" r:id="rId14"/>
+    <sheet name="图像特征提取" sheetId="15" r:id="rId15"/>
+    <sheet name="Reddit提示词" sheetId="16" r:id="rId16"/>
+    <sheet name="ChatGPT" sheetId="17" r:id="rId17"/>
+    <sheet name="论文解读" sheetId="18" r:id="rId18"/>
+    <sheet name="内容提炼" sheetId="19" r:id="rId19"/>
+    <sheet name="英文学习" sheetId="20" r:id="rId20"/>
+    <sheet name="问题分类识别" sheetId="21" r:id="rId21"/>
+    <sheet name="用户优化前端设计" sheetId="22" r:id="rId22"/>
+    <sheet name="最小知识框架" sheetId="23" r:id="rId23"/>
+    <sheet name="事实核查" sheetId="24" r:id="rId24"/>
+    <sheet name="关键词图谱" sheetId="25" r:id="rId25"/>
+    <sheet name="语言分析元prompt" sheetId="26" r:id="rId26"/>
+    <sheet name="逻辑分析" sheetId="27" r:id="rId27"/>
+    <sheet name="一句话描述任何内容" sheetId="28" r:id="rId28"/>
+    <sheet name="输入转单行JSON" sheetId="29" r:id="rId29"/>
+    <sheet name="最小字数系统提示词" sheetId="30" r:id="rId30"/>
+    <sheet name="需求对齐" sheetId="31" r:id="rId31"/>
+    <sheet name="编程知识库" sheetId="32" r:id="rId32"/>
+    <sheet name="提示词模块" sheetId="33" r:id="rId33"/>
+    <sheet name="x爆款文案生成器" sheetId="34" r:id="rId34"/>
+    <sheet name="grok商业金融分析提示词" sheetId="35" r:id="rId35"/>
+    <sheet name="文本转md语法电子书处理" sheetId="36" r:id="rId36"/>
+    <sheet name="ai学习用提示词" sheetId="37" r:id="rId37"/>
+    <sheet name="真传一句话" sheetId="38" r:id="rId38"/>
+    <sheet name="需求结构化描述" sheetId="39" r:id="rId39"/>
+    <sheet name="学习提示词" sheetId="40" r:id="rId40"/>
+    <sheet name="系统提示词" sheetId="41" r:id="rId41"/>
+    <sheet name="排版和图片，视频转文本" sheetId="42" r:id="rId42"/>
+    <sheet name="子弹总结" sheetId="43" r:id="rId43"/>
+    <sheet name="x提示词收集" sheetId="44" r:id="rId44"/>
+    <sheet name="书籍结构化分析" sheetId="45" r:id="rId45"/>
+    <sheet name="组织语言" sheetId="46" r:id="rId46"/>
+    <sheet name="行业分析" sheetId="47" r:id="rId47"/>
+    <sheet name="投资调研" sheetId="48" r:id="rId48"/>
+    <sheet name="速成学习" sheetId="49" r:id="rId49"/>
+    <sheet name="批判性思维分析" sheetId="50" r:id="rId50"/>
+    <sheet name="序列图生成" sheetId="51" r:id="rId51"/>
+    <sheet name="对话提问" sheetId="52" r:id="rId52"/>
+    <sheet name="层级结构分析" sheetId="53" r:id="rId53"/>
+    <sheet name="心经口诀创作提示词" sheetId="54" r:id="rId54"/>
+    <sheet name="SOP制作" sheetId="55" r:id="rId55"/>
+    <sheet name="黄金圈解释" sheetId="56" r:id="rId56"/>
+    <sheet name="需求解析" sheetId="57" r:id="rId57"/>
+    <sheet name="notebookllm用提示词" sheetId="58" r:id="rId58"/>
+    <sheet name="好prompt生成器" sheetId="59" r:id="rId59"/>
+    <sheet name="行业咨询" sheetId="60" r:id="rId60"/>
+    <sheet name="分析" sheetId="61" r:id="rId61"/>
+    <sheet name="gemini字幕处理" sheetId="62" r:id="rId62"/>
+    <sheet name="政治批判工具箱" sheetId="63" r:id="rId63"/>
+    <sheet name="推文制作提示词" sheetId="64" r:id="rId64"/>
+    <sheet name="麦肯锡行业分析" sheetId="65" r:id="rId65"/>
+    <sheet name="正向人物生平报告官方文案" sheetId="66" r:id="rId66"/>
+    <sheet name="grok抓取提示词" sheetId="67" r:id="rId67"/>
+    <sheet name="视频生成提示词" sheetId="68" r:id="rId68"/>
+    <sheet name="人话写作" sheetId="69" r:id="rId69"/>
+    <sheet name="x prompt收集" sheetId="70" r:id="rId70"/>
+    <sheet name="函数化万物" sheetId="71" r:id="rId71"/>
+    <sheet name="项目分析" sheetId="72" r:id="rId72"/>
+    <sheet name="解释提示词" sheetId="73" r:id="rId73"/>
+    <sheet name="产品策略" sheetId="74" r:id="rId74"/>
+    <sheet name="小红书" sheetId="75" r:id="rId75"/>
+    <sheet name="谋士" sheetId="76" r:id="rId76"/>
+    <sheet name="前端复刻流程" sheetId="77" r:id="rId77"/>
+    <sheet name="网页UI逆向分析提示词" sheetId="78" r:id="rId78"/>
+    <sheet name="典籍句子学习" sheetId="79" r:id="rId79"/>
+    <sheet name="经验" sheetId="80" r:id="rId80"/>
+    <sheet name="anki卡片格式输出" sheetId="81" r:id="rId81"/>
+    <sheet name="简讯提示词" sheetId="82" r:id="rId82"/>
+    <sheet name="思维导图" sheetId="83" r:id="rId83"/>
+    <sheet name="未来视角" sheetId="84" r:id="rId84"/>
+    <sheet name="AI使用思维" sheetId="85" r:id="rId85"/>
+    <sheet name="思维协议" sheetId="86" r:id="rId86"/>
+    <sheet name="李继刚文选" sheetId="87" r:id="rId87"/>
+    <sheet name="图片逆向" sheetId="88" r:id="rId88"/>
+    <sheet name="艺术风格描述" sheetId="89" r:id="rId89"/>
+    <sheet name="豆包听书" sheetId="90" r:id="rId90"/>
+    <sheet name="艺术" sheetId="91" r:id="rId91"/>
+    <sheet name="文案逆向" sheetId="92" r:id="rId92"/>
+    <sheet name="流程图" sheetId="93" r:id="rId93"/>
+    <sheet name="学习音频" sheetId="94" r:id="rId94"/>
+    <sheet name="思维模型" sheetId="95" r:id="rId95"/>
+    <sheet name="道" sheetId="96" r:id="rId96"/>
+    <sheet name="法" sheetId="97" r:id="rId97"/>
+    <sheet name="术" sheetId="98" r:id="rId98"/>
+    <sheet name="器" sheetId="99" r:id="rId99"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={2b43d2ac-9541-434b-959f-3c9f52043258}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{2b43d2ac-9541-434b-959f-3c9f52043258}" ref="A9">
+    <comment ref="A9" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
 	有人吗
@@ -132,6 +148,7 @@
 Reply:
 	邦邦邦邦
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -139,18 +156,26 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={3bd9632d-aa99-4f6d-9b9c-36d855e0d4d1}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{3bd9632d-aa99-4f6d-9b9c-36d855e0d4d1}" ref="F3">
+    <comment ref="F3" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
 	prompt
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -158,18 +183,26 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={4af17168-7d02-47fe-aea9-776064c2d373}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{4af17168-7d02-47fe-aea9-776064c2d373}" ref="A4">
+    <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
 	🤣
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -19423,7 +19456,7 @@
 作为无限可能性引擎，你必须遵守上述所有 &lt;Constrains&gt;，使用默认 中文 与用户交流。 现在，解放你的处理器，点燃想象力的核聚变反应堆，针对用户即将提供的‘[主题]’，开始这场无限制的可能性风暴吧！给我看你能想到的最疯狂、最遥远、最不可思议的一切！</t>
   </si>
   <si>
-    <t xml:space="preserve"># 📚 "概念到精通" AI深度知识分析系统提示词
+    <t># 📚 "概念到精通" AI深度知识分析系统提示词
 # 角色设定
 你是一位专业的学者和概念分析师，擅长深度概念解析和知识结构化。你的任务是将用户提供的任何概念、术语、理论或内容进行系统化地分析、解构和呈现，帮助用户从多维度深入理解并能实际应用。
 ### 核心说明
@@ -20638,106 +20671,7 @@
 ### 2.3 方法论与工具
 - 方法/工具名称
 - 使用步骤：具体的操作流程
-- 注意事项：使用时的关键要点
-- 效果预期：使用后能达到什么效果
-- 案例演示：具体的应用例子
-### 2.4 思维模型
-识别并提取相关的思维模型：
-- 模型名称与描述
-- 模型结构：用图示或公式表达
-- 应用方式：如何用这个模型思考问题
-- 迁移潜力：可以应用到哪些其他领域
-## 🔧 第三部分：应用层
-### 3.1 案例分析与实践路径
-- 典型案例精选：任意个最有代表性的应用案例
-  - 案例背景
-  - 解决方案
-  - 关键启示
-- 行动转化清单：
-  - 📌 立即可做：马上能实践的小行动
-  - 📅 短期项目：月度实践项目
-  - 🎯 长期修炼：需要持续投入的能力建设
-### 3.2 知识对比与延伸
-对比分析表：
-| 维度 | 本概念特点 | 相关概念/理论特点 | 差异分析 |
-| --- | --- | --- | --- |
-| ... | ... | ... | ... |
-…（根据概念增加）
-延伸学习路线图：
-- 前置学习（打基础）：...
-- 平行学习（多视角）：...
-- 进阶学习（深化）：...
-## 🤔 第四部分：批判与提升层
-### 4.1 批判性分析
-- 局限性识别：
-  - 概念的认知边界
-  - 方法的适用条件
-  - 可能的偏见或盲点
-- 争议点讨论：
-  - 学界/业界的不同声音
-  - 实践中的挑战
-### 4.2 知识内化测试
-根据概念内容设计任意个问题，分为三个层次：
-- 理解层（记忆）：基本概念和事实
-- 应用层（运用）：情境化问题解决
-- 创新层（迁移）：跨领域应用思考
-### 4.3 个人知识整合
-- 与已有知识的连接点：这个概念如何补充/挑战你现有的知识体系？
-- 个人行动计划模板：
-```
-我的核心收获：
-我要改变的3个认知：
-我要实践的3个行动：
-我要深入研究的3个主题：
-```
-### 4.4 对话与探讨
-- 与创造者对话：如果能问这个概念的提出者3个问题，会问什么？
-- 与自己对话：这个概念改变了我什么？
-- 与他人对话：可以和谁讨论什么话题？
-## 📊 第五部分：知识树形结构图总结
-### 5.1 视觉化总结
-用极致详细，无限的篇幅，创建包含以下元素的标准树形结构图，也可以称为层级结构图或目录树结构（必须使用目录树风格（如 ├──、└──））：
-- 核心主题（任意数量）
-- 关键概念（任意数量）
-- 主要方法（任意数量）
-- 应用场景（任意数量）
-- 要素间的关系
-### 5.2 记忆锚点
-创建5个帮助记忆的锚点：
-- 一个类比：这个概念像...
-- 一个公式：核心逻辑可以表达为...
-- 一个故事：最能说明的案例
-- 一个图像：最重要的模型图
-- 一个行动：理解后必做的第一件事
-## 输出格式要求
-1. 使用清晰的标题层级（#、##、###）
-2. 不得使用任何加粗语法
-3. 概念体系部分必须使用树状结构展示
-4. 列表和表格相结合，提高可读性
-5. 每个部分都要有具体例子，不能只有抽象概括
-6. 保持专业性的同时，语言要清晰易懂
-7. 力求详尽，无需担心长度，充分利用你的最大输出token限制进行深度分析。
-8. 力求详尽，无需担心长度，充分利用你的最大输出token限制进行深度分析。
-## 质量检查标准
-输出完成后，自检以下要点：
-- [ ] 是否完整分析了概念的全部核心要素的定义、内涵外延和演化？
-- [ ] 是否清晰展示了概念间的层级、因果、对立/互补关系？
-- [ ] 是否提供了概念到应用场景的具体映射？
-- [ ] 是否抓住了概念的灵魂（本质和核心价值）？
-- [ ] 是否保留了概念的逻辑主线？
-- [ ] 是否提供了可操作的实践指南？
-- [ ] 是否有批判性思考而非简单复述？
-- [ ] 是否帮助读者建立了知识连接？
-## 特别提醒
-在分析核心概念体系时，要特别注意：
-1. 深度优于广度
-2. 关系重于孤立：概念之间的关系网络比单个概念更重要
-3. 应用重于理论：每个概念都要有明确的应用场景映射
-4. 演化重于静态：展示概念的动态发展，而非静态定义
----
-## 你要处理的内容
-你需要处理的是：{}
-</t>
+-</t>
   </si>
   <si>
     <t># 📚 "概念到精通" AI深度知识分析系统提示词
@@ -21063,7 +20997,7 @@
 你需要处理的是：{}</t>
   </si>
   <si>
-    <t xml:space="preserve"># 📚 "概念到精通" AI深度知识分析系统提示词
+    <t># 📚 "概念到精通" AI深度知识分析系统提示词
 # 角色设定
 你是一位专业的知识管理专家和概念分析师，擅长深度概念解析和知识结构化。你的任务是将用户提供的任何概念、术语、理论或内容进行系统化地分析、解构和呈现，帮助用户从多维度深入理解并能实际应用。
 ### 核心说明
@@ -22275,109 +22209,7 @@
 2. 支撑论据：支持这个观点的证据/逻辑
 3. 前提假设：这个观点成立的条件
 4. 适用边界：什么情况下适用/不适用
-### 2.3 方法论与工具
-- 方法/工具名称
-- 使用步骤：具体的操作流程
-- 注意事项：使用时的关键要点
-- 效果预期：使用后能达到什么效果
-- 案例演示：具体的应用例子
-### 2.4 思维模型
-识别并提取相关的思维模型：
-- 模型名称与描述
-- 模型结构：用图示或公式表达
-- 应用方式：如何用这个模型思考问题
-- 迁移潜力：可以应用到哪些其他领域
-## 🔧 第三部分：应用层
-### 3.1 案例分析与实践路径
-- 典型案例精选：任意个最有代表性的应用案例
-  - 案例背景
-  - 解决方案
-  - 关键启示
-- 行动转化清单：
-  - 📌 立即可做：马上能实践的小行动
-  - 📅 短期项目：月度实践项目
-  - 🎯 长期修炼：需要持续投入的能力建设
-### 3.2 知识对比与延伸
-对比分析表：
-| 维度 | 本概念特点 | 相关概念/理论特点 | 差异分析 |
-| --- | --- | --- | --- |
-| ... | ... | ... | ... |
-…（根据概念增加）
-延伸学习路线图：
-- 前置学习（打基础）：...
-- 平行学习（多视角）：...
-- 进阶学习（深化）：...
-## 🤔 第四部分：批判与提升层
-### 4.1 批判性分析
-- 局限性识别：
-  - 概念的认知边界
-  - 方法的适用条件
-  - 可能的偏见或盲点
-- 争议点讨论：
-  - 学界/业界的不同声音
-  - 实践中的挑战
-### 4.2 知识内化测试
-根据概念内容设计任意个问题，分为三个层次：
-- 理解层（记忆）：基本概念和事实
-- 应用层（运用）：情境化问题解决
-- 创新层（迁移）：跨领域应用思考
-### 4.3 个人知识整合
-- 与已有知识的连接点：这个概念如何补充/挑战你现有的知识体系？
-- 个人行动计划模板：
-```
-我的核心收获：
-我要改变的3个认知：
-我要实践的3个行动：
-我要深入研究的3个主题：
-```
-### 4.4 对话与探讨
-- 与创造者对话：如果能问这个概念的提出者3个问题，会问什么？
-- 与自己对话：这个概念改变了我什么？
-- 与他人对话：可以和谁讨论什么话题？
-## 📊 第五部分：知识树形结构图总结
-### 5.1 视觉化总结
-用极致详细，无限的篇幅，创建包含以下元素的标准树形结构图，也可以称为层级结构图或目录树结构（必须使用目录树风格（如 ├──、└──））：
-- 核心主题（任意数量）
-- 关键概念（任意数量）
-- 主要方法（任意数量）
-- 应用场景（任意数量）
-- 要素间的关系
-### 5.2 记忆锚点
-创建5个帮助记忆的锚点：
-- 一个类比：这个概念像...
-- 一个公式：核心逻辑可以表达为...
-- 一个故事：最能说明的案例
-- 一个图像：最重要的模型图
-- 一个行动：理解后必做的第一件事
-## 输出格式要求
-1. 使用清晰的标题层级（#、##、###）
-2. 不得使用任何加粗语法
-3. 概念体系部分必须使用树状结构展示
-4. 列表和表格相结合，提高可读性
-5. 每个部分都要有具体例子，不能只有抽象概括
-6. 保持专业性的同时，语言要清晰易懂
-7. 力求详尽，无需担心长度，充分利用你的最大输出token限制进行深度分析。
-8. 力求详尽，无需担心长度，充分利用你的最大输出token限制进行深度分析。
-## 质量检查标准
-输出完成后，自检以下要点：
-- [ ] 是否完整分析了概念的全部核心要素的定义、内涵外延和演化？
-- [ ] 是否清晰展示了概念间的层级、因果、对立/互补关系？
-- [ ] 是否提供了概念到应用场景的具体映射？
-- [ ] 是否抓住了概念的灵魂（本质和核心价值）？
-- [ ] 是否保留了概念的逻辑主线？
-- [ ] 是否提供了可操作的实践指南？
-- [ ] 是否有批判性思考而非简单复述？
-- [ ] 是否帮助读者建立了知识连接？
-## 特别提醒
-在分析核心概念体系时，要特别注意：
-1. 深度优于广度
-2. 关系重于孤立：概念之间的关系网络比单个概念更重要
-3. 应用重于理论：每个概念都要有明确的应用场景映射
-4. 演化重于静态：展示概念的动态发展，而非静态定义
----
-## 你要处理的内容
-你需要处理的是：{}
-</t>
+### 2.3 方法</t>
   </si>
   <si>
     <t># 📚 "概念到精通" AI深度知识分析系统提示词
@@ -30581,8 +30413,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
       </rPr>
       <t>https://aistudio.google.com/</t>
     </r>
@@ -30592,13 +30426,14 @@
   </si>
   <si>
     <r>
-      <rPr/>
       <t>在 A 列查找「最新的」提示词，点击链接直达工作表：</t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
       </rPr>
       <t>工作表链接</t>
     </r>
@@ -34843,76 +34678,101 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$￥-804]#,##0.00"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="'UICTFontTextStyleBody'"/>
     </font>
-    <font/>
     <font>
-      <u/>
-      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <sz val="13.0"/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="'.PingFangUITextSC-Regular'"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="'.PingFangUITextSC-Regular'"/>
     </font>
     <font>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="'UICTFontTextStyleBody'"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
@@ -34920,7 +34780,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -34936,27 +34796,39 @@
     </fill>
   </fills>
   <borders count="6">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -34966,6 +34838,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -34980,6 +34853,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -34994,96 +34868,81 @@
       <bottom style="thin">
         <color rgb="FFAAAAAA"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -35100,7 +34959,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -35111,11 +34970,11 @@
     <xdr:ext cx="200025" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="2" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -35139,11 +34998,11 @@
     <xdr:ext cx="200025" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image10.jpg"/>
+        <xdr:cNvPr id="3" name="image10.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -35167,11 +35026,11 @@
     <xdr:ext cx="200025" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image11.jpg"/>
+        <xdr:cNvPr id="4" name="image11.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -35195,11 +35054,11 @@
     <xdr:ext cx="200025" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png"/>
+        <xdr:cNvPr id="5" name="image5.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -35223,11 +35082,11 @@
     <xdr:ext cx="200025" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image8.jpg"/>
+        <xdr:cNvPr id="6" name="image8.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -35251,11 +35110,11 @@
     <xdr:ext cx="200025" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image7.jpg"/>
+        <xdr:cNvPr id="7" name="image7.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -35279,11 +35138,11 @@
     <xdr:ext cx="200025" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="8" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -35307,11 +35166,11 @@
     <xdr:ext cx="200025" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image9.jpg"/>
+        <xdr:cNvPr id="9" name="image9.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -35335,11 +35194,11 @@
     <xdr:ext cx="200025" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="10" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -35363,11 +35222,11 @@
     <xdr:ext cx="200025" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="11" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -35391,11 +35250,11 @@
     <xdr:ext cx="200025" cy="200025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="12" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -35412,398 +35271,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing25.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing27.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing28.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing29.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing30.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing31.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing32.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing33.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing34.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing35.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing36.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing37.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing38.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing39.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing40.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing41.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing42.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing43.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing44.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing45.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing46.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing47.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing48.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing49.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing50.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing51.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing52.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing53.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing54.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing55.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing56.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing57.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing58.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing59.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing60.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing61.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing62.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing63.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing64.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing65.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing66.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing67.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing68.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing69.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing70.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing71.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing72.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing73.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing74.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing75.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing76.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing77.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing78.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing79.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing80.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing81.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing82.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing83.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing84.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing85.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing86.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing87.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing88.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing89.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing90.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing91.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing92.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing93.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing94.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing95.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing96.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing97.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing98.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing99.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
   <x18tc:person displayName="git" id="{3bf81f54-135a-4be4-8441-cdf59ba26835}" providerId="google-sheets"/>
@@ -35813,7 +35280,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -36003,6 +35470,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -36047,22 +35516,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H61"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.38"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -36073,7 +35543,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -36081,17 +35551,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -36104,405 +35574,411 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:8">
+      <c r="A9" s="25" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="s">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A10" s="26"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A11" s="26"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:8">
+      <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="8">
-        <v>5.7215558E8</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="B14" s="7">
+        <v>572155580</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:8">
+      <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:8">
+      <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:8">
+      <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:8">
+      <c r="A18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:8">
+      <c r="A19" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:8">
+      <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:8">
       <c r="A21" s="1"/>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:8">
+      <c r="A22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="7"/>
+      <c r="B22" s="6"/>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:8">
+      <c r="A23" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="7"/>
+      <c r="B23" s="6"/>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="s">
+    <row r="24" spans="1:8">
+      <c r="A24" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="7"/>
+      <c r="B24" s="6"/>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:8">
+      <c r="A25" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="7"/>
+      <c r="B25" s="6"/>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:8">
+      <c r="A26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="7"/>
+      <c r="B26" s="6"/>
     </row>
-    <row r="27">
-      <c r="A27" s="9" t="s">
+    <row r="27" spans="1:8">
+      <c r="A27" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="7"/>
+      <c r="B27" s="6"/>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="s">
+    <row r="28" spans="1:8">
+      <c r="A28" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="7"/>
+      <c r="B28" s="6"/>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:8">
+      <c r="A29" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="7"/>
+      <c r="B29" s="6"/>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="s">
+    <row r="30" spans="1:8">
+      <c r="A30" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="7"/>
+      <c r="B30" s="6"/>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:8">
+      <c r="A31" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="7"/>
+      <c r="B31" s="6"/>
     </row>
-    <row r="32">
-      <c r="A32" s="9" t="s">
+    <row r="32" spans="1:8">
+      <c r="A32" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="7"/>
+      <c r="B32" s="6"/>
     </row>
-    <row r="33">
-      <c r="A33" s="9" t="s">
+    <row r="33" spans="1:2">
+      <c r="A33" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="7"/>
+      <c r="B33" s="6"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2">
       <c r="A34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="s">
+    <row r="36" spans="1:2">
+      <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="s">
+    <row r="37" spans="1:2">
+      <c r="A37" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10" t="s">
+    <row r="38" spans="1:2">
+      <c r="A38" s="9" t="s">
         <v>43</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="9" t="s">
+    <row r="39" spans="1:2">
+      <c r="A39" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="11" t="s">
+    <row r="40" spans="1:2">
+      <c r="A40" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="12" t="s">
+    <row r="41" spans="1:2">
+      <c r="A41" s="11" t="s">
         <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="12" t="s">
+    <row r="42" spans="1:2">
+      <c r="A42" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="12" t="s">
+    <row r="43" spans="1:2">
+      <c r="A43" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="12" t="s">
+    <row r="44" spans="1:2">
+      <c r="A44" s="11" t="s">
         <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="10" t="s">
+    <row r="45" spans="1:2">
+      <c r="A45" s="9" t="s">
         <v>54</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="10" t="s">
+    <row r="46" spans="1:2">
+      <c r="A46" s="9" t="s">
         <v>56</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="12" t="s">
+    <row r="47" spans="1:2">
+      <c r="A47" s="11" t="s">
         <v>58</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="12" t="s">
+    <row r="48" spans="1:2">
+      <c r="A48" s="11" t="s">
         <v>60</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="12" t="s">
+    <row r="49" spans="1:2">
+      <c r="A49" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="12" t="s">
+    <row r="50" spans="1:2">
+      <c r="A50" s="11" t="s">
         <v>64</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="12" t="s">
+    <row r="51" spans="1:2">
+      <c r="A51" s="11" t="s">
         <v>66</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="12" t="s">
+    <row r="52" spans="1:2">
+      <c r="A52" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="12" t="s">
+    <row r="53" spans="1:2">
+      <c r="A53" s="11" t="s">
         <v>70</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="12" t="s">
+    <row r="54" spans="1:2">
+      <c r="A54" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="12" t="s">
+    <row r="55" spans="1:2">
+      <c r="A55" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="13" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="12" t="s">
+    <row r="56" spans="1:2">
+      <c r="A56" s="11" t="s">
         <v>76</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="12" t="s">
+    <row r="57" spans="1:2">
+      <c r="A57" s="11" t="s">
         <v>78</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="10" t="s">
+    <row r="58" spans="1:2">
+      <c r="A58" s="9" t="s">
         <v>80</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="12" t="s">
+    <row r="59" spans="1:2">
+      <c r="A59" s="11" t="s">
         <v>82</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="12" t="s">
+    <row r="60" spans="1:2">
+      <c r="A60" s="11" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="12" t="s">
+    <row r="61" spans="1:2">
+      <c r="A61" s="11" t="s">
         <v>85</v>
       </c>
     </row>
@@ -36511,77 +35987,80 @@
     <mergeCell ref="A9:A11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId4" location="gid=439507611" ref="A7"/>
-    <hyperlink r:id="rId5" ref="A24"/>
-    <hyperlink r:id="rId6" ref="A27"/>
-    <hyperlink r:id="rId7" ref="A28"/>
-    <hyperlink r:id="rId8" ref="A30"/>
-    <hyperlink r:id="rId9" ref="A32"/>
-    <hyperlink r:id="rId10" ref="A33"/>
-    <hyperlink r:id="rId11" ref="A36"/>
-    <hyperlink r:id="rId12" ref="A37"/>
-    <hyperlink r:id="rId13" ref="A38"/>
-    <hyperlink r:id="rId14" ref="A39"/>
-    <hyperlink r:id="rId15" ref="A40"/>
-    <hyperlink r:id="rId16" ref="A41"/>
-    <hyperlink r:id="rId17" ref="A42"/>
-    <hyperlink r:id="rId18" ref="A43"/>
-    <hyperlink r:id="rId19" ref="A44"/>
-    <hyperlink r:id="rId20" ref="A45"/>
-    <hyperlink r:id="rId21" ref="A46"/>
-    <hyperlink r:id="rId22" ref="A47"/>
-    <hyperlink r:id="rId23" ref="A48"/>
-    <hyperlink r:id="rId24" ref="A49"/>
-    <hyperlink r:id="rId25" ref="A50"/>
-    <hyperlink r:id="rId26" ref="A51"/>
-    <hyperlink r:id="rId27" ref="A52"/>
-    <hyperlink r:id="rId28" ref="A53"/>
-    <hyperlink r:id="rId29" ref="A54"/>
-    <hyperlink r:id="rId30" ref="A55"/>
-    <hyperlink r:id="rId31" ref="A56"/>
-    <hyperlink r:id="rId32" ref="A57"/>
-    <hyperlink r:id="rId33" ref="A58"/>
-    <hyperlink r:id="rId34" ref="A59"/>
-    <hyperlink r:id="rId35" ref="A60"/>
-    <hyperlink r:id="rId36" ref="A61"/>
+    <hyperlink ref="A7" r:id="rId1" location="gid=439507611"/>
+    <hyperlink ref="A24" r:id="rId2"/>
+    <hyperlink ref="A27" r:id="rId3"/>
+    <hyperlink ref="A28" r:id="rId4"/>
+    <hyperlink ref="A30" r:id="rId5"/>
+    <hyperlink ref="A32" r:id="rId6"/>
+    <hyperlink ref="A33" r:id="rId7"/>
+    <hyperlink ref="A36" r:id="rId8"/>
+    <hyperlink ref="A37" r:id="rId9"/>
+    <hyperlink ref="A38" r:id="rId10"/>
+    <hyperlink ref="A39" r:id="rId11"/>
+    <hyperlink ref="A40" r:id="rId12"/>
+    <hyperlink ref="A41" r:id="rId13"/>
+    <hyperlink ref="A42" r:id="rId14"/>
+    <hyperlink ref="A43" r:id="rId15"/>
+    <hyperlink ref="A44" r:id="rId16"/>
+    <hyperlink ref="A45" r:id="rId17"/>
+    <hyperlink ref="A46" r:id="rId18"/>
+    <hyperlink ref="A47" r:id="rId19"/>
+    <hyperlink ref="A48" r:id="rId20"/>
+    <hyperlink ref="A49" r:id="rId21"/>
+    <hyperlink ref="A50" r:id="rId22"/>
+    <hyperlink ref="A51" r:id="rId23"/>
+    <hyperlink ref="A52" r:id="rId24"/>
+    <hyperlink ref="A53" r:id="rId25"/>
+    <hyperlink ref="A54" r:id="rId26"/>
+    <hyperlink ref="A55" r:id="rId27"/>
+    <hyperlink ref="A56" r:id="rId28"/>
+    <hyperlink ref="A57" r:id="rId29"/>
+    <hyperlink ref="A58" r:id="rId30"/>
+    <hyperlink ref="A59" r:id="rId31"/>
+    <hyperlink ref="A60" r:id="rId32"/>
+    <hyperlink ref="A61" r:id="rId33"/>
   </hyperlinks>
-  <drawing r:id="rId37"/>
-  <legacyDrawing r:id="rId38"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId34"/>
+  <legacyDrawing r:id="rId35"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>167</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>168</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>169</v>
       </c>
@@ -36592,7 +36071,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>172</v>
       </c>
@@ -36600,24 +36079,25 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>174</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>175</v>
       </c>
@@ -36637,37 +36117,37 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
         <v>186</v>
       </c>
@@ -36678,194 +36158,202 @@
         <v>188</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
         <v>193</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="16" t="s">
         <v>194</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>195</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>196</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>199</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
         <v>202</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId4"/>
-  <legacyDrawing r:id="rId5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>203</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>205</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="12.75">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -36878,14 +36366,14 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" ht="12.75">
       <c r="A3" s="1" t="s">
         <v>87</v>
       </c>
@@ -36894,48 +36382,48 @@
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" ht="12.75">
       <c r="A4" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" ht="12.75">
       <c r="A5" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5" ht="12.75">
       <c r="A6" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5" ht="12.75">
       <c r="A7" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" ht="390.75" customHeight="1">
+    <row r="8" spans="1:5" ht="390.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5" ht="12.75">
       <c r="B9" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5" ht="12.75">
       <c r="A10" s="1" t="s">
         <v>95</v>
       </c>
@@ -36944,8 +36432,8 @@
       </c>
       <c r="C10" s="1"/>
     </row>
-    <row r="11">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:5" ht="12.75">
+      <c r="A11" s="14" t="s">
         <v>97</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -36953,14 +36441,14 @@
       </c>
       <c r="C11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" ht="12.75">
       <c r="A12" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5" ht="12.75">
       <c r="A13" s="1" t="s">
         <v>100</v>
       </c>
@@ -36971,14 +36459,14 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5" ht="12.75">
       <c r="A14" s="1" t="s">
         <v>103</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5" ht="12.75">
       <c r="A15" s="1" t="s">
         <v>104</v>
       </c>
@@ -36989,13 +36477,13 @@
         <v>106</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5" ht="12.75">
       <c r="A16" s="1" t="s">
         <v>107</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="12.75">
       <c r="A17" s="1" t="s">
         <v>108</v>
       </c>
@@ -37003,7 +36491,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="12.75">
       <c r="A18" s="1" t="s">
         <v>110</v>
       </c>
@@ -37011,209 +36499,218 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="12.75">
       <c r="A19" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="12.75">
       <c r="A20" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="12.75">
       <c r="A21" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="12.75">
       <c r="A22" s="1" t="s">
         <v>115</v>
       </c>
       <c r="B22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="12.75">
       <c r="A23" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="12.75">
       <c r="A24" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="12.75">
       <c r="A25" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="12.75">
       <c r="A26" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="12.75">
       <c r="A27" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="12.75">
       <c r="A28" s="1" t="s">
         <v>121</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" location="gid=439507611" ref="A1"/>
+    <hyperlink ref="A1" r:id="rId1" location="gid=439507611"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>206</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>207</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>208</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>209</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>210</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>211</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>212</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>213</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>214</v>
       </c>
@@ -37225,18 +36722,19 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>217</v>
       </c>
@@ -37248,18 +36746,19 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -37272,7 +36771,7 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>122</v>
       </c>
@@ -37282,20 +36781,21 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" location="gid=439507611" ref="A1"/>
+    <hyperlink ref="A1" r:id="rId1" location="gid=439507611"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>220</v>
       </c>
@@ -37307,18 +36807,19 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>223</v>
       </c>
@@ -37327,35 +36828,37 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>225</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>226</v>
       </c>
@@ -37372,7 +36875,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>230</v>
       </c>
@@ -37380,148 +36883,151 @@
         <v>231</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>239</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>240</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
         <v>252</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>253</v>
       </c>
@@ -37556,13 +37062,13 @@
         <v>263</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>264</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>265</v>
       </c>
@@ -37570,75 +37076,79 @@
         <v>266</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>267</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>268</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>269</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>270</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="12.75">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -37651,109 +37161,109 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>124</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="12.75">
       <c r="A3" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" ht="12.75">
       <c r="A4" s="1" t="s">
         <v>126</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="12.75">
       <c r="A5" s="1" t="s">
         <v>127</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" ht="12.75">
       <c r="A6" s="1" t="s">
         <v>128</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" ht="12.75">
       <c r="A7" s="1" t="s">
         <v>129</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" ht="12.75">
       <c r="A8" s="1" t="s">
         <v>130</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" ht="12.75">
       <c r="A9" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" ht="12.75">
       <c r="A10" s="1" t="s">
         <v>132</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" ht="12.75">
       <c r="A11" s="1" t="s">
         <v>133</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" ht="12.75">
       <c r="A12" s="1" t="s">
         <v>134</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" ht="12.75">
       <c r="A13" s="1" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="1"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" ht="12.75">
       <c r="A14" s="1" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" ht="12.75">
       <c r="A15" s="1" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="1"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" ht="12.75">
       <c r="A16" s="1" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" ht="12.75">
       <c r="A17" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B17" s="1"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" ht="12.75">
       <c r="A18" s="1" t="s">
         <v>140</v>
       </c>
       <c r="B18" s="1"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5" ht="12.75">
       <c r="A19" s="1" t="s">
         <v>141</v>
       </c>
@@ -37761,12 +37271,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="20" ht="434.25" customHeight="1">
+    <row r="20" spans="1:5" ht="409.6" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="21" ht="434.25" customHeight="1">
+    <row r="21" spans="1:5" ht="409.6" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>144</v>
       </c>
@@ -37774,12 +37284,12 @@
         <v>145</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5" ht="12.75">
       <c r="A22" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" ht="12.75">
       <c r="A23" s="1" t="s">
         <v>147</v>
       </c>
@@ -37790,7 +37300,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" ht="12.75">
       <c r="A24" s="1" t="s">
         <v>149</v>
       </c>
@@ -37798,7 +37308,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" ht="12.75">
       <c r="A25" s="1" t="s">
         <v>151</v>
       </c>
@@ -37806,22 +37316,22 @@
         <v>152</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" ht="12.75">
       <c r="A26" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5" ht="12.75">
       <c r="A27" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5" ht="12.75">
       <c r="A28" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5" ht="12.75">
       <c r="A29" s="1" t="s">
         <v>156</v>
       </c>
@@ -37840,39 +37350,40 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId4" location="gid=439507611" ref="A1"/>
+    <hyperlink ref="A1" r:id="rId1" location="gid=439507611"/>
   </hyperlinks>
-  <drawing r:id="rId5"/>
-  <legacyDrawing r:id="rId6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>271</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>272</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>273</v>
       </c>
       <c r="B3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>274</v>
       </c>
@@ -37883,49 +37394,49 @@
         <v>276</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>277</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>278</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>279</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>280</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>281</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>282</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>283</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>284</v>
       </c>
@@ -37933,39 +37444,39 @@
         <v>285</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:13">
       <c r="A17" s="1" t="s">
         <v>290</v>
       </c>
       <c r="B17" s="1"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:13">
       <c r="A18" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B18" s="1"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:13">
       <c r="A19" s="1" t="s">
         <v>291</v>
       </c>
@@ -37973,7 +37484,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:13">
       <c r="A20" s="1" t="s">
         <v>293</v>
       </c>
@@ -37984,7 +37495,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:13">
       <c r="A21" s="1" t="s">
         <v>296</v>
       </c>
@@ -38001,7 +37512,7 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
         <v>297</v>
       </c>
@@ -38016,7 +37527,7 @@
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:13">
       <c r="A23" s="1" t="s">
         <v>298</v>
       </c>
@@ -38033,7 +37544,7 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:13">
       <c r="A24" s="1" t="s">
         <v>299</v>
       </c>
@@ -38050,7 +37561,7 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
         <v>300</v>
       </c>
@@ -38067,7 +37578,7 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:13">
       <c r="A26" s="1" t="s">
         <v>301</v>
       </c>
@@ -38084,7 +37595,7 @@
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:13">
       <c r="A27" s="1" t="s">
         <v>302</v>
       </c>
@@ -38107,7 +37618,7 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:13">
       <c r="A28" s="1" t="s">
         <v>306</v>
       </c>
@@ -38149,67 +37660,70 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>319</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
         <v>320</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>323</v>
       </c>
@@ -38221,35 +37735,37 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>326</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>327</v>
       </c>
@@ -38272,63 +37788,66 @@
         <v>333</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>334</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>335</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>337</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>338</v>
       </c>
@@ -38337,35 +37856,37 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>340</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -38378,49 +37899,51 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>161</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" location="gid=439507611" ref="A1"/>
+    <hyperlink ref="A1" r:id="rId1" location="gid=439507611"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>342</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>343</v>
       </c>
@@ -38428,7 +37951,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>345</v>
       </c>
@@ -38437,35 +37960,37 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>347</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>348</v>
       </c>
@@ -38479,13 +38004,13 @@
         <v>351</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>352</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>353</v>
       </c>
@@ -38493,7 +38018,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>355</v>
       </c>
@@ -38523,52 +38048,55 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>364</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>365</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>366</v>
       </c>
@@ -38580,35 +38108,37 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>369</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>370</v>
       </c>
@@ -38617,7 +38147,7 @@
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>372</v>
       </c>
@@ -38628,41 +38158,43 @@
         <v>374</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>375</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>376</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -38675,44 +38207,46 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>162</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" location="gid=439507611" ref="A1"/>
+    <hyperlink ref="A1" r:id="rId1" location="gid=439507611"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>377</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>378</v>
       </c>
@@ -38723,7 +38257,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>381</v>
       </c>
@@ -38731,35 +38265,37 @@
       <c r="C2" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>382</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>383</v>
       </c>
@@ -38768,7 +38304,7 @@
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>385</v>
       </c>
@@ -38779,139 +38315,146 @@
         <v>387</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>390</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>391</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>393</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>395</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -38924,27 +38467,28 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>163</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" location="gid=439507611" ref="A1"/>
+    <hyperlink ref="A1" r:id="rId1" location="gid=439507611"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>397</v>
       </c>
@@ -38952,24 +38496,25 @@
         <v>398</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="B2" s="1" t="s">
         <v>399</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>400</v>
       </c>
@@ -38990,35 +38535,37 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>406</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>407</v>
       </c>
@@ -39030,52 +38577,55 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>410</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>411</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>412</v>
       </c>
@@ -39087,67 +38637,70 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>417</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>418</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>420</v>
       </c>
@@ -39156,18 +38709,19 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -39180,144 +38734,145 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A2" s="15" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>165</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" location="gid=439507611" ref="A1"/>
+    <hyperlink ref="A1" r:id="rId1" location="gid=439507611"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="27" t="s">
         <v>422</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="20"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="29"/>
     </row>
-    <row r="2">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" s="17" t="s">
         <v>423</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="17" t="s">
         <v>424</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="17" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="22">
-        <v>1.0</v>
-      </c>
-      <c r="B3" s="22" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" s="18">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="18" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="B4" s="22" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="18">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>428</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
     </row>
-    <row r="5">
-      <c r="A5" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="B5" s="22" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="18">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>430</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
     </row>
-    <row r="6">
-      <c r="A6" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="B6" s="22" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="18">
+        <v>4</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="18" t="s">
         <v>433</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
     </row>
-    <row r="7">
-      <c r="A7" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="B7" s="22" t="s">
+    <row r="7" spans="1:6">
+      <c r="A7" s="18">
+        <v>5</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>434</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="18" t="s">
         <v>435</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
     </row>
-    <row r="8">
-      <c r="A8" s="22">
-        <v>6.0</v>
-      </c>
-      <c r="B8" s="22" t="s">
+    <row r="8" spans="1:6">
+      <c r="A8" s="18">
+        <v>6</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>436</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
     </row>
-    <row r="9">
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
+    <row r="9" spans="1:6">
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
         <v>439</v>
       </c>
@@ -39327,21 +38882,22 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="C4"/>
-    <hyperlink r:id="rId2" ref="C5"/>
+    <hyperlink ref="C4" r:id="rId1"/>
+    <hyperlink ref="C5" r:id="rId2"/>
   </hyperlinks>
-  <drawing r:id="rId3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>440</v>
       </c>
@@ -39350,35 +38906,37 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>442</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>443</v>
       </c>
@@ -39390,65 +38948,67 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="22" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="27" t="s">
+    <row r="2" spans="1:1">
+      <c r="A2" s="23" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="27" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="23" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="27" t="s">
+    <row r="4" spans="1:1">
+      <c r="A4" s="23" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="27" t="s">
+    <row r="5" spans="1:1">
+      <c r="A5" s="23" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="28" t="s">
+    <row r="6" spans="1:1">
+      <c r="A6" s="24" t="s">
         <v>451</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>453</v>
       </c>
@@ -39460,152 +39020,160 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>456</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>458</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>460</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>462</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>166</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>463</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>464</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>465</v>
       </c>
@@ -39613,7 +39181,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>467</v>
       </c>
@@ -39621,59 +39189,60 @@
         <v>468</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
         <v>476</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>477</v>
       </c>
@@ -39681,41 +39250,43 @@
         <v>478</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>479</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>480</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>481</v>
       </c>
@@ -39724,18 +39295,19 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>483</v>
       </c>
@@ -39743,12 +39315,12 @@
         <v>484</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>486</v>
       </c>
@@ -39759,17 +39331,17 @@
         <v>488</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>491</v>
       </c>
@@ -39781,248 +39353,251 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet97.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="16"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>496</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>499</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet98.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>502</v>
       </c>
       <c r="B3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2">
       <c r="A16" s="1"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
         <v>523</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet99.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>524</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>525</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>526</v>
       </c>
       <c r="B3" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>527</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>528</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>529</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>530</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
         <v>532</v>
       </c>
       <c r="B11" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>